--- a/tests/Full_Accounting_Test_Case.xlsx
+++ b/tests/Full_Accounting_Test_Case.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
   <si>
     <t>Category</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Sheet Name (Config)</t>
   </si>
   <si>
-    <t>Account Type</t>
+    <t>Sheet Type</t>
   </si>
   <si>
     <t>Flip Polarity? (Yes/No)</t>
@@ -51,6 +51,9 @@
     <t>Header Row</t>
   </si>
   <si>
+    <t>1099 Type</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
@@ -123,6 +126,15 @@
     <t>Services</t>
   </si>
   <si>
+    <t>Owner Equity</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
     <t>Contractor 1099</t>
   </si>
   <si>
@@ -159,25 +171,25 @@
     <t>Version ID</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>3.0.142</t>
   </si>
   <si>
     <t>Git SHA</t>
   </si>
   <si>
-    <t>5bab65fd3b3bfd11deb9b900711e268940bb6749</t>
+    <t>d307335a4428c01d3d82d91d7307ace54f8c30ce</t>
   </si>
   <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>1/20/2026, 2:48:12 PM</t>
+    <t>9/25/2026, 8:23:11 PM</t>
   </si>
   <si>
     <t>--- Import History ---</t>
   </si>
   <si>
-    <t>Import at 1/20/2026, 2:48:12 PM</t>
+    <t>Import at 9/25/2026, 8:23:12 PM</t>
   </si>
   <si>
     <t xml:space="preserve">Command: node load_transactions.js tests/example_bank.csv bank Test_Accounting.xlsx --clear
@@ -229,6 +241,9 @@
     <t>Consulting Services</t>
   </si>
   <si>
+    <t>Major Contract Work</t>
+  </si>
+  <si>
     <t>Mystery Corp</t>
   </si>
   <si>
@@ -239,9 +254,6 @@
   </si>
   <si>
     <t>Uncategorized Expense</t>
-  </si>
-  <si>
-    <t>Major Contract Work</t>
   </si>
   <si>
     <t>Member</t>
@@ -659,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
@@ -673,7 +685,7 @@
     <col min="12" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -710,172 +722,175 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
+      <c r="N1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
-      </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="6:7" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="N11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -900,7 +915,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C1" s="3">
         <f>SUM(C4:C10000)</f>
@@ -908,7 +923,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4">
         <f>SUBTOTAL(109, C4:C10000)</f>
@@ -916,13 +931,13 @@
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>0</v>
@@ -931,16 +946,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -948,19 +963,19 @@
         <v>45658</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C4">
         <v>5000</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G4" t="s">
         <v>4</v>
@@ -977,19 +992,19 @@
         <v>45662</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>-1500</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G5" t="s">
         <v>4</v>
@@ -1006,19 +1021,19 @@
         <v>45667</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>2500</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G6" t="s">
         <v>4</v>
@@ -1032,16 +1047,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>45682</v>
+        <v>45684</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>-737.5</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>4</v>
@@ -1050,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
         <v>4</v>
@@ -1058,16 +1073,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>45683</v>
+        <v>45682</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
@@ -1076,7 +1091,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
         <v>4</v>
@@ -1084,16 +1099,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>45684</v>
+        <v>45683</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C9">
-        <v>-737.5</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E9" t="s">
         <v>4</v>
@@ -1102,7 +1117,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H9" t="s">
         <v>4</v>
@@ -1147,7 +1162,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D1" s="3">
         <f>SUM(D4:D10000)</f>
@@ -1155,7 +1170,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D2" s="4">
         <f>SUBTOTAL(109, D4:D10000)</f>
@@ -1163,16 +1178,16 @@
     </row>
     <row r="3" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>0</v>
@@ -1181,22 +1196,22 @@
         <v>1</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1207,19 +1222,19 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>15.5</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
@@ -1245,19 +1260,19 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s">
         <v>4</v>
@@ -1283,19 +1298,19 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s">
         <v>4</v>
@@ -1336,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1347,22 +1362,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1370,10 +1385,10 @@
         <v>45658</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>1000</v>
@@ -1384,19 +1399,53 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>45658</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>45677</v>
       </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3">
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
         <v>50</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45677</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1426,39 +1475,39 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1466,18 +1515,18 @@
     </row>
     <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/tests/Full_Accounting_Test_Case.xlsx
+++ b/tests/Full_Accounting_Test_Case.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="86">
   <si>
     <t>Category</t>
   </si>
@@ -51,6 +51,9 @@
     <t>Header Row</t>
   </si>
   <si>
+    <t>End Balance</t>
+  </si>
+  <si>
     <t>1099 Type</t>
   </si>
   <si>
@@ -177,27 +180,30 @@
     <t>Git SHA</t>
   </si>
   <si>
-    <t>d307335a4428c01d3d82d91d7307ace54f8c30ce</t>
+    <t>08f61282a92ff4007f08418c5e623f1acc0b7708</t>
   </si>
   <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>9/25/2026, 8:23:11 PM</t>
+    <t>10/29/2026, 8:59:58 AM</t>
   </si>
   <si>
     <t>--- Import History ---</t>
   </si>
   <si>
-    <t>Import at 9/25/2026, 8:23:12 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Command: node load_transactions.js tests/example_bank.csv bank Test_Accounting.xlsx --clear
+    <t>Import at 10/29/2026, 8:59:58 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command: node load_transactions.js tests/example_bank.csv bank C:\Users\raysa\AppData\Local\Temp\llc-test-ysTJwN\Test_Accounting.xlsx --clear
 Input: tests/example_bank.csv
 Target Sheet: Bank Transactions</t>
   </si>
   <si>
-    <t xml:space="preserve">Command: node load_transactions.js tests/example_cc.csv cc Test_Accounting.xlsx --clear
+    <t>Import at 10/29/2026, 8:59:59 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command: node load_transactions.js tests/example_cc.csv cc C:\Users\raysa\AppData\Local\Temp\llc-test-ysTJwN\Test_Accounting.xlsx --clear
 Input: tests/example_cc.csv
 Target Sheet: Credit Card Transactions</t>
   </si>
@@ -682,7 +688,7 @@
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="12" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -722,175 +728,184 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
       <c r="N1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>6362.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5">
         <v>3</v>
       </c>
+      <c r="M5">
+        <v>180.5</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -915,7 +930,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="3">
         <f>SUM(C4:C10000)</f>
@@ -923,7 +938,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2" s="4">
         <f>SUBTOTAL(109, C4:C10000)</f>
@@ -931,13 +946,13 @@
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>0</v>
@@ -946,16 +961,16 @@
         <v>1</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -963,19 +978,19 @@
         <v>45658</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>5000</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
         <v>4</v>
@@ -992,19 +1007,19 @@
         <v>45662</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>-1500</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G5" t="s">
         <v>4</v>
@@ -1021,19 +1036,19 @@
         <v>45667</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6">
         <v>2500</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s">
         <v>4</v>
@@ -1050,13 +1065,13 @@
         <v>45684</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7">
         <v>-737.5</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>4</v>
@@ -1065,7 +1080,7 @@
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
         <v>4</v>
@@ -1076,13 +1091,13 @@
         <v>45682</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
@@ -1091,7 +1106,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
         <v>4</v>
@@ -1102,7 +1117,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>50</v>
@@ -1162,7 +1177,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D1" s="3">
         <f>SUM(D4:D10000)</f>
@@ -1170,7 +1185,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="4">
         <f>SUBTOTAL(109, D4:D10000)</f>
@@ -1178,16 +1193,16 @@
     </row>
     <row r="3" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>0</v>
@@ -1196,22 +1211,22 @@
         <v>1</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1222,19 +1237,19 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>15.5</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
@@ -1260,19 +1275,19 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s">
         <v>4</v>
@@ -1298,19 +1313,19 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s">
         <v>4</v>
@@ -1362,22 +1377,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1385,10 +1400,10 @@
         <v>45658</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>1000</v>
@@ -1402,10 +1417,10 @@
         <v>45658</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1419,10 +1434,10 @@
         <v>45677</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -1436,10 +1451,10 @@
         <v>45677</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1475,39 +1490,39 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1515,18 +1530,18 @@
     </row>
     <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
